--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260914.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260914.xlsx
@@ -887,17 +887,17 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>5,250,520</t>
+          <t>3,401,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>3,401,000</t>
+          <t>5,250,520</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,816,000</t>
+          <t>372,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>762,000</t>
+          <t>5,670,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,670,000</t>
+          <t>762,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>372,000</t>
+          <t>1,816,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>928,659</t>
+          <t>1,186,441</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,186,441</t>
+          <t>3,449,981</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>3,449,981</t>
+          <t>928,659</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>1,366,384</t>
+          <t>2,573,703</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>2,573,703</t>
+          <t>1,366,384</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>577,000</t>
+          <t>144,386</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>144,386</t>
+          <t>577,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>386,000</t>
+          <t>92,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>92,000</t>
+          <t>386,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,174,076</t>
+          <t>180,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>180,000</t>
+          <t>1,174,076</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>797,000</t>
+          <t>769,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>493,000</t>
+          <t>797,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>4,915,956</t>
+          <t>493,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>769,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>4,915,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>328,000</t>
+          <t>150</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,7 +1987,7 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>202610WVHFV6F</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>202610WVHFV6F</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>328,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2097,17 +2097,17 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>176,000</t>
+          <t>155,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>155,000</t>
+          <t>176,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
